--- a/artfynd/A 44635-2025 artfynd.xlsx
+++ b/artfynd/A 44635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557139</v>
+        <v>121557136</v>
       </c>
       <c r="B2" t="n">
-        <v>4770</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396224</v>
+        <v>396003</v>
       </c>
       <c r="R2" t="n">
-        <v>6377646</v>
+        <v>6377596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,53 +776,67 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557141</v>
+        <v>121635989</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100087</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källhult, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396166</v>
+        <v>396150</v>
       </c>
       <c r="R3" t="n">
-        <v>6377695</v>
+        <v>6377562</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,88 +890,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Torge Gerwin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>FNT0023 Källhult</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635977</v>
+        <v>121557139</v>
       </c>
       <c r="B4" t="n">
-        <v>56259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källhult, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396151</v>
+        <v>396224</v>
       </c>
       <c r="R4" t="n">
-        <v>6377559</v>
+        <v>6377646</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:40</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>04:40</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,79 +987,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>FNT0023 Källhult</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635989</v>
+        <v>121557141</v>
       </c>
       <c r="B5" t="n">
-        <v>56529</v>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100087</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källhult, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396150</v>
+        <v>396166</v>
       </c>
       <c r="R5" t="n">
-        <v>6377562</v>
+        <v>6377695</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>06:30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,54 +1088,53 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen, Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>FNT0023 Källhult</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635953</v>
+        <v>121635955</v>
       </c>
       <c r="B6" t="n">
-        <v>56280</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1194,7 +1149,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1203,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396150</v>
+        <v>396231</v>
       </c>
       <c r="R6" t="n">
-        <v>6377562</v>
+        <v>6377504</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,12 +1233,7 @@
         <v>121635959</v>
       </c>
       <c r="B7" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,6 +1353,384 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121635971</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>396231</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6377504</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121635977</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>396151</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6377559</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121635953</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Källhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>396150</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6377562</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44635-2025 artfynd.xlsx
+++ b/artfynd/A 44635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>FNT0023 Källhult</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635989</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>FNT0023 Källhult</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557139</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>FNT0023 Källhult</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557141</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635955</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635959</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635971</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635977</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,8 +1776,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>